--- a/converted_files/837/cob-prov-payera.xlsx
+++ b/converted_files/837/cob-prov-payera.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b4ffa</t>
+          <t>69e82c69836d7d05c9a05800</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2543,7 +2543,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b4ffa</t>
+          <t>69e82c69836d7d05c9a05800</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2930,7 +2930,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b4ffa</t>
+          <t>69e82c69836d7d05c9a05800</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/cob-prov-payera.xlsx
+++ b/converted_files/837/cob-prov-payera.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b4ffa</t>
+          <t>69efef06ad4799caa7f5e483</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2543,7 +2543,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b4ffa</t>
+          <t>69efef06ad4799caa7f5e483</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2930,7 +2930,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b4ffa</t>
+          <t>69efef06ad4799caa7f5e483</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/cob-prov-payera.xlsx
+++ b/converted_files/837/cob-prov-payera.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a05800</t>
+          <t>6a04cb3c618f76c4f7b196b1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2543,7 +2543,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a05800</t>
+          <t>6a04cb3c618f76c4f7b196b1</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2930,7 +2930,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a05800</t>
+          <t>6a04cb3c618f76c4f7b196b1</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/cob-prov-payera.xlsx
+++ b/converted_files/837/cob-prov-payera.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b196b1</t>
+          <t>6a04cc5c1ef26d534baf41bf</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2543,7 +2543,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b196b1</t>
+          <t>6a04cc5c1ef26d534baf41bf</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2930,7 +2930,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b196b1</t>
+          <t>6a04cc5c1ef26d534baf41bf</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/cob-prov-payera.xlsx
+++ b/converted_files/837/cob-prov-payera.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf41bf</t>
+          <t>6a0614def8d6a2fc74349009</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2543,7 +2543,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf41bf</t>
+          <t>6a0614def8d6a2fc74349009</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2930,7 +2930,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf41bf</t>
+          <t>6a0614def8d6a2fc74349009</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/cob-prov-payera.xlsx
+++ b/converted_files/837/cob-prov-payera.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74349009</t>
+          <t>6a32cb6597613a0e499096e2</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2543,7 +2543,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74349009</t>
+          <t>6a32cb6597613a0e499096e2</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2930,7 +2930,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74349009</t>
+          <t>6a32cb6597613a0e499096e2</t>
         </is>
       </c>
       <c r="B4"/>
